--- a/artfynd/A 16123-2026 artfynd.xlsx
+++ b/artfynd/A 16123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133036105</v>
+        <v>133036111</v>
       </c>
       <c r="B2" t="n">
         <v>79329</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402795</v>
+        <v>402735</v>
       </c>
       <c r="R2" t="n">
-        <v>6825888</v>
+        <v>6825821</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133036111</v>
+        <v>133036105</v>
       </c>
       <c r="B4" t="n">
         <v>79329</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402735</v>
+        <v>402795</v>
       </c>
       <c r="R4" t="n">
-        <v>6825821</v>
+        <v>6825888</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133036073</v>
+        <v>133036079</v>
       </c>
       <c r="B6" t="n">
         <v>79087</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402572</v>
+        <v>402749</v>
       </c>
       <c r="R6" t="n">
-        <v>6825764</v>
+        <v>6825878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133036079</v>
+        <v>133036073</v>
       </c>
       <c r="B7" t="n">
         <v>79087</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402749</v>
+        <v>402572</v>
       </c>
       <c r="R7" t="n">
-        <v>6825878</v>
+        <v>6825764</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,45 +1257,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133036030</v>
+        <v>133036059</v>
       </c>
       <c r="B8" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402655</v>
+        <v>402611</v>
       </c>
       <c r="R8" t="n">
-        <v>6825813</v>
+        <v>6825851</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133036074</v>
+        <v>133036030</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402612</v>
+        <v>402655</v>
       </c>
       <c r="R9" t="n">
-        <v>6825742</v>
+        <v>6825813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,53 +1556,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133036059</v>
+        <v>133036074</v>
       </c>
       <c r="B11" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402611</v>
+        <v>402612</v>
       </c>
       <c r="R11" t="n">
-        <v>6825851</v>
+        <v>6825742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133036031</v>
+        <v>133036044</v>
       </c>
       <c r="B12" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402676</v>
+        <v>402624</v>
       </c>
       <c r="R12" t="n">
-        <v>6825820</v>
+        <v>6825848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133036044</v>
+        <v>133036031</v>
       </c>
       <c r="B13" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402624</v>
+        <v>402676</v>
       </c>
       <c r="R13" t="n">
-        <v>6825848</v>
+        <v>6825820</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133036023</v>
+        <v>133036029</v>
       </c>
       <c r="B15" t="n">
         <v>79948</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402479</v>
+        <v>402631</v>
       </c>
       <c r="R15" t="n">
-        <v>6825791</v>
+        <v>6825844</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133036029</v>
+        <v>133036023</v>
       </c>
       <c r="B16" t="n">
         <v>79948</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402631</v>
+        <v>402479</v>
       </c>
       <c r="R16" t="n">
-        <v>6825844</v>
+        <v>6825791</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133036082</v>
+        <v>133036019</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2254,21 +2254,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>402804</v>
+        <v>402701</v>
       </c>
       <c r="R18" t="n">
-        <v>6825894</v>
+        <v>6825708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,45 +2437,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133036019</v>
+        <v>133036054</v>
       </c>
       <c r="B20" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>402701</v>
+        <v>402682</v>
       </c>
       <c r="R20" t="n">
-        <v>6825708</v>
+        <v>6825914</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2534,7 +2542,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133036054</v>
+        <v>133036056</v>
       </c>
       <c r="B21" t="n">
         <v>57142</v>
@@ -2577,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402682</v>
+        <v>402473</v>
       </c>
       <c r="R21" t="n">
-        <v>6825914</v>
+        <v>6825788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2639,53 +2647,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133036056</v>
+        <v>133036082</v>
       </c>
       <c r="B22" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402473</v>
+        <v>402804</v>
       </c>
       <c r="R22" t="n">
-        <v>6825788</v>
+        <v>6825894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133036081</v>
+        <v>133036100</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79329</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>402788</v>
+        <v>402699</v>
       </c>
       <c r="R24" t="n">
-        <v>6825896</v>
+        <v>6825854</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133036100</v>
+        <v>133036081</v>
       </c>
       <c r="B26" t="n">
-        <v>79329</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>402699</v>
+        <v>402788</v>
       </c>
       <c r="R26" t="n">
-        <v>6825854</v>
+        <v>6825896</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,10 +3229,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133036078</v>
+        <v>133036020</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79948</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3240,21 +3240,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>402726</v>
+        <v>402690</v>
       </c>
       <c r="R28" t="n">
-        <v>6825877</v>
+        <v>6825706</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133036020</v>
+        <v>133036078</v>
       </c>
       <c r="B32" t="n">
-        <v>79948</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>402690</v>
+        <v>402726</v>
       </c>
       <c r="R32" t="n">
-        <v>6825706</v>
+        <v>6825877</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133036077</v>
+        <v>133036041</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79919</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3725,21 +3725,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>402508</v>
+        <v>402672</v>
       </c>
       <c r="R33" t="n">
-        <v>6825841</v>
+        <v>6825910</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133036041</v>
+        <v>133036077</v>
       </c>
       <c r="B34" t="n">
-        <v>79919</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>402672</v>
+        <v>402508</v>
       </c>
       <c r="R34" t="n">
-        <v>6825910</v>
+        <v>6825841</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3908,53 +3908,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133036057</v>
+        <v>133036095</v>
       </c>
       <c r="B35" t="n">
-        <v>57142</v>
+        <v>79329</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>402565</v>
+        <v>402648</v>
       </c>
       <c r="R35" t="n">
-        <v>6825861</v>
+        <v>6825618</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4013,7 +4005,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036058</v>
+        <v>133036057</v>
       </c>
       <c r="B36" t="n">
         <v>57142</v>
@@ -4056,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>402615</v>
+        <v>402565</v>
       </c>
       <c r="R36" t="n">
-        <v>6825849</v>
+        <v>6825861</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4118,45 +4110,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133036080</v>
+        <v>133036058</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>402781</v>
+        <v>402615</v>
       </c>
       <c r="R37" t="n">
-        <v>6825888</v>
+        <v>6825849</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133036095</v>
+        <v>133036080</v>
       </c>
       <c r="B39" t="n">
-        <v>79329</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>402648</v>
+        <v>402781</v>
       </c>
       <c r="R39" t="n">
-        <v>6825618</v>
+        <v>6825888</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133036104</v>
+        <v>133036021</v>
       </c>
       <c r="B40" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>402719</v>
+        <v>402545</v>
       </c>
       <c r="R40" t="n">
-        <v>6825867</v>
+        <v>6825874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,10 +4506,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133036021</v>
+        <v>133036104</v>
       </c>
       <c r="B41" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>402545</v>
+        <v>402719</v>
       </c>
       <c r="R41" t="n">
-        <v>6825874</v>
+        <v>6825867</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5592,6 +5592,1763 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133036060</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>402623</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6825846</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133036085</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57133</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>402520</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6825816</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133036114</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>402750</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6825828</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133036033</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79948</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>402739</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6825874</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133036071</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>402718</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6825866</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133036070</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>402702</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6825886</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133036053</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>402697</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6825856</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>133036062</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>402738</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6825841</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>133036119</v>
+      </c>
+      <c r="B60" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>402643</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6825819</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>133036069</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>402665</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6825816</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133036047</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79919</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>402804</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6825894</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133036049</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>402692</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6825851</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>133036042</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79919</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>402462</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6825823</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>133036050</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>402577</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6825812</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>133036118</v>
+      </c>
+      <c r="B66" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>402624</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6825913</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>133036051</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>402664</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6825645</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>133036052</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>402687</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6825707</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16123-2026 artfynd.xlsx
+++ b/artfynd/A 16123-2026 artfynd.xlsx
@@ -2437,53 +2437,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133036054</v>
+        <v>133036082</v>
       </c>
       <c r="B20" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>402682</v>
+        <v>402804</v>
       </c>
       <c r="R20" t="n">
-        <v>6825914</v>
+        <v>6825894</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2542,7 +2534,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133036056</v>
+        <v>133036054</v>
       </c>
       <c r="B21" t="n">
         <v>57142</v>
@@ -2585,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402473</v>
+        <v>402682</v>
       </c>
       <c r="R21" t="n">
-        <v>6825788</v>
+        <v>6825914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,45 +2639,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133036082</v>
+        <v>133036056</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402804</v>
+        <v>402473</v>
       </c>
       <c r="R22" t="n">
-        <v>6825894</v>
+        <v>6825788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133036020</v>
+        <v>133036027</v>
       </c>
       <c r="B28" t="n">
         <v>79948</v>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>402690</v>
+        <v>402621</v>
       </c>
       <c r="R28" t="n">
-        <v>6825706</v>
+        <v>6825845</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133036116</v>
+        <v>133036046</v>
       </c>
       <c r="B29" t="n">
-        <v>93201</v>
+        <v>79919</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>402698</v>
+        <v>402789</v>
       </c>
       <c r="R29" t="n">
-        <v>6825796</v>
+        <v>6825895</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133036027</v>
+        <v>133036078</v>
       </c>
       <c r="B30" t="n">
-        <v>79948</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3434,21 +3434,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>402621</v>
+        <v>402726</v>
       </c>
       <c r="R30" t="n">
-        <v>6825845</v>
+        <v>6825877</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133036046</v>
+        <v>133036020</v>
       </c>
       <c r="B31" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3531,21 +3531,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>402789</v>
+        <v>402690</v>
       </c>
       <c r="R31" t="n">
-        <v>6825895</v>
+        <v>6825706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133036078</v>
+        <v>133036116</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>93201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>402726</v>
+        <v>402698</v>
       </c>
       <c r="R32" t="n">
-        <v>6825877</v>
+        <v>6825796</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 16123-2026 artfynd.xlsx
+++ b/artfynd/A 16123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,7 +3229,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133036027</v>
+        <v>133036020</v>
       </c>
       <c r="B28" t="n">
         <v>79948</v>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>402621</v>
+        <v>402690</v>
       </c>
       <c r="R28" t="n">
-        <v>6825845</v>
+        <v>6825706</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133036046</v>
+        <v>133036116</v>
       </c>
       <c r="B29" t="n">
-        <v>79919</v>
+        <v>93201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>402789</v>
+        <v>402698</v>
       </c>
       <c r="R29" t="n">
-        <v>6825895</v>
+        <v>6825796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133036078</v>
+        <v>133036027</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79948</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3434,21 +3434,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>402726</v>
+        <v>402621</v>
       </c>
       <c r="R30" t="n">
-        <v>6825877</v>
+        <v>6825845</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133036020</v>
+        <v>133036046</v>
       </c>
       <c r="B31" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3531,21 +3531,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>402690</v>
+        <v>402789</v>
       </c>
       <c r="R31" t="n">
-        <v>6825706</v>
+        <v>6825895</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133036116</v>
+        <v>133036078</v>
       </c>
       <c r="B32" t="n">
-        <v>93201</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>402698</v>
+        <v>402726</v>
       </c>
       <c r="R32" t="n">
-        <v>6825796</v>
+        <v>6825877</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133036095</v>
+        <v>133036076</v>
       </c>
       <c r="B35" t="n">
-        <v>79329</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>402648</v>
+        <v>402671</v>
       </c>
       <c r="R35" t="n">
-        <v>6825618</v>
+        <v>6825919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4005,53 +4005,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036057</v>
+        <v>133036080</v>
       </c>
       <c r="B36" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>402565</v>
+        <v>402781</v>
       </c>
       <c r="R36" t="n">
-        <v>6825861</v>
+        <v>6825888</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4110,53 +4102,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133036058</v>
+        <v>133036095</v>
       </c>
       <c r="B37" t="n">
-        <v>57142</v>
+        <v>79329</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>402615</v>
+        <v>402648</v>
       </c>
       <c r="R37" t="n">
-        <v>6825849</v>
+        <v>6825618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4215,45 +4199,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133036076</v>
+        <v>133036057</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>402671</v>
+        <v>402565</v>
       </c>
       <c r="R38" t="n">
-        <v>6825919</v>
+        <v>6825861</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4312,45 +4304,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133036080</v>
+        <v>133036058</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>402781</v>
+        <v>402615</v>
       </c>
       <c r="R39" t="n">
-        <v>6825888</v>
+        <v>6825849</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -7349,6 +7349,5817 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>133109719</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>402691</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6825776</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>133108969</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>402730</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6825832</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>133109721</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>402810</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6825794</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133112188</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79919</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>402775</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6825802</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>133112192</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>402694</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6825714</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>133112183</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79948</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>402740</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6825910</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>133112214</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78995</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>353</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>402724</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6825783</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>133108957</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>402665</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6825701</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>133108956</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79948</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>402671</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6825689</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133112191</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>402669</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6825647</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>133108973</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>402819</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6825855</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>133108965</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78336</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>402810</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6825852</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>133109714</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>402597</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6825728</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>133109723</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>402815</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6825863</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>133108966</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>402720</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6825770</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>133108972</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>402802</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6825850</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>133112212</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>402803</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6825848</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>133112206</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>402700</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6825887</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>133112215</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78336</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>402733</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6825919</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>133108970</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>402812</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6825827</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>133112210</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>402750</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6825892</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>133109706</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79919</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>402604</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6825731</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>133112185</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79948</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>402814</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6825873</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>133108960</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>402802</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6825824</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>133108968</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>402718</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6825795</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>133108959</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>402720</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6825751</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>133112202</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79086</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>402674</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6825913</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>133112207</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>402731</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6825856</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>133112200</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79086</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>402719</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6825867</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>133108964</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79086</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>402721</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6825752</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>133108962</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79086</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>402802</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6825824</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>133108967</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>402719</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6825791</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>133112197</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>402778</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6825767</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>133112182</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79948</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>402723</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6825890</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>133112208</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>402747</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6825862</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>133109707</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>402583</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6825567</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>133108954</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79948</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>402672</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6825661</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>133109724</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>402811</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6825861</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>133108981</v>
+      </c>
+      <c r="B107" t="n">
+        <v>78995</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>353</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>402836</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6825888</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>133108961</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>402798</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6825844</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>133112189</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79919</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>402752</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6825895</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>133112209</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>402689</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6825895</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>133112199</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79086</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>402724</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6825890</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>133108963</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79086</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>402805</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6825842</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>133109722</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>402811</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6825852</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>133108982</v>
+      </c>
+      <c r="B114" t="n">
+        <v>78336</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>402799</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6825819</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>133109716</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79086</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>402436</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6825493</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>133109718</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>402694</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6825772</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>133112198</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>402674</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6825913</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>133112205</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>402684</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6825707</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>133108974</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>402840</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6825887</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>133112194</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>402728</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6825870</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>133112211</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Stor-Vargtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>402791</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6825853</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>133108955</v>
+      </c>
+      <c r="B122" t="n">
+        <v>79948</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Brunnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>402804</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6825841</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16123-2026 artfynd.xlsx
+++ b/artfynd/A 16123-2026 artfynd.xlsx
@@ -1257,45 +1257,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133036030</v>
+        <v>133036059</v>
       </c>
       <c r="B8" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402655</v>
+        <v>402611</v>
       </c>
       <c r="R8" t="n">
-        <v>6825813</v>
+        <v>6825851</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133036106</v>
+        <v>133036030</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402810</v>
+        <v>402655</v>
       </c>
       <c r="R9" t="n">
-        <v>6825893</v>
+        <v>6825813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,53 +1459,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133036059</v>
+        <v>133036106</v>
       </c>
       <c r="B10" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402611</v>
+        <v>402810</v>
       </c>
       <c r="R10" t="n">
-        <v>6825851</v>
+        <v>6825893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133036044</v>
+        <v>133036031</v>
       </c>
       <c r="B12" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402624</v>
+        <v>402676</v>
       </c>
       <c r="R12" t="n">
-        <v>6825848</v>
+        <v>6825820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133036031</v>
+        <v>133036044</v>
       </c>
       <c r="B13" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402676</v>
+        <v>402624</v>
       </c>
       <c r="R13" t="n">
-        <v>6825820</v>
+        <v>6825848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133036084</v>
+        <v>133036029</v>
       </c>
       <c r="B14" t="n">
-        <v>57136</v>
+        <v>79952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,42 +1858,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402521</v>
+        <v>402631</v>
       </c>
       <c r="R14" t="n">
-        <v>6825808</v>
+        <v>6825844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133036103</v>
+        <v>133036023</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1955,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402700</v>
+        <v>402479</v>
       </c>
       <c r="R15" t="n">
-        <v>6825867</v>
+        <v>6825791</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133036029</v>
+        <v>133036103</v>
       </c>
       <c r="B16" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,21 +2052,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402631</v>
+        <v>402700</v>
       </c>
       <c r="R16" t="n">
-        <v>6825844</v>
+        <v>6825867</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,10 +2138,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133036023</v>
+        <v>133036084</v>
       </c>
       <c r="B17" t="n">
-        <v>79952</v>
+        <v>57136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2157,34 +2149,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>402479</v>
+        <v>402521</v>
       </c>
       <c r="R17" t="n">
-        <v>6825791</v>
+        <v>6825808</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133036082</v>
+        <v>133036019</v>
       </c>
       <c r="B18" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2254,21 +2254,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>402804</v>
+        <v>402701</v>
       </c>
       <c r="R18" t="n">
-        <v>6825894</v>
+        <v>6825708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133036019</v>
+        <v>133036024</v>
       </c>
       <c r="B19" t="n">
         <v>79952</v>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>402701</v>
+        <v>402477</v>
       </c>
       <c r="R19" t="n">
-        <v>6825708</v>
+        <v>6825770</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,45 +2437,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133036024</v>
+        <v>133036056</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>402477</v>
+        <v>402473</v>
       </c>
       <c r="R20" t="n">
-        <v>6825770</v>
+        <v>6825788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,53 +2647,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133036056</v>
+        <v>133036082</v>
       </c>
       <c r="B22" t="n">
-        <v>57145</v>
+        <v>79091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402473</v>
+        <v>402804</v>
       </c>
       <c r="R22" t="n">
-        <v>6825788</v>
+        <v>6825894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133036020</v>
+        <v>133036116</v>
       </c>
       <c r="B28" t="n">
-        <v>79952</v>
+        <v>93206</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>402690</v>
+        <v>402698</v>
       </c>
       <c r="R28" t="n">
-        <v>6825706</v>
+        <v>6825796</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133036116</v>
+        <v>133036020</v>
       </c>
       <c r="B29" t="n">
-        <v>93206</v>
+        <v>79952</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>402698</v>
+        <v>402690</v>
       </c>
       <c r="R29" t="n">
-        <v>6825796</v>
+        <v>6825706</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133036076</v>
+        <v>133036095</v>
       </c>
       <c r="B35" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>402671</v>
+        <v>402648</v>
       </c>
       <c r="R35" t="n">
-        <v>6825919</v>
+        <v>6825618</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4005,45 +4005,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036080</v>
+        <v>133036057</v>
       </c>
       <c r="B36" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>402781</v>
+        <v>402565</v>
       </c>
       <c r="R36" t="n">
-        <v>6825888</v>
+        <v>6825861</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4102,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133036095</v>
+        <v>133036076</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>402648</v>
+        <v>402671</v>
       </c>
       <c r="R37" t="n">
-        <v>6825618</v>
+        <v>6825919</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4199,53 +4207,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133036057</v>
+        <v>133036080</v>
       </c>
       <c r="B38" t="n">
-        <v>57145</v>
+        <v>79091</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>402565</v>
+        <v>402781</v>
       </c>
       <c r="R38" t="n">
-        <v>6825861</v>
+        <v>6825888</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4805,53 +4805,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133036063</v>
+        <v>133036034</v>
       </c>
       <c r="B44" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>402600</v>
+        <v>402778</v>
       </c>
       <c r="R44" t="n">
-        <v>6825837</v>
+        <v>6825894</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4884,11 +4876,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk tjäderspillning inom en radie av 15 meter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4915,10 +4902,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133036034</v>
+        <v>133036099</v>
       </c>
       <c r="B45" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4926,21 +4913,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4950,10 +4937,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>402778</v>
+        <v>402608</v>
       </c>
       <c r="R45" t="n">
-        <v>6825894</v>
+        <v>6825849</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5012,45 +4999,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133036099</v>
+        <v>133036063</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>402608</v>
+        <v>402600</v>
       </c>
       <c r="R46" t="n">
-        <v>6825849</v>
+        <v>6825837</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5083,6 +5078,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk tjäderspillning inom en radie av 15 meter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5400,10 +5400,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133036025</v>
+        <v>133036096</v>
       </c>
       <c r="B50" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5411,21 +5411,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>402503</v>
+        <v>402697</v>
       </c>
       <c r="R50" t="n">
-        <v>6825785</v>
+        <v>6825752</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133036096</v>
+        <v>133036025</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>402697</v>
+        <v>402503</v>
       </c>
       <c r="R51" t="n">
-        <v>6825752</v>
+        <v>6825785</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6321,10 +6321,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133036062</v>
+        <v>133036119</v>
       </c>
       <c r="B59" t="n">
-        <v>57145</v>
+        <v>93206</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6332,31 +6332,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6364,10 +6359,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>402738</v>
+        <v>402643</v>
       </c>
       <c r="R59" t="n">
-        <v>6825841</v>
+        <v>6825819</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6408,6 +6403,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6426,10 +6422,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133036119</v>
+        <v>133036062</v>
       </c>
       <c r="B60" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6437,26 +6433,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6464,10 +6465,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>402643</v>
+        <v>402738</v>
       </c>
       <c r="R60" t="n">
-        <v>6825819</v>
+        <v>6825841</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6508,7 +6509,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6527,10 +6527,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133036069</v>
+        <v>133036049</v>
       </c>
       <c r="B61" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6538,16 +6538,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6560,7 +6560,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>402665</v>
+        <v>402692</v>
       </c>
       <c r="R61" t="n">
-        <v>6825816</v>
+        <v>6825851</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133036049</v>
+        <v>133036047</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>79923</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6643,42 +6643,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>402692</v>
+        <v>402804</v>
       </c>
       <c r="R62" t="n">
-        <v>6825851</v>
+        <v>6825894</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6737,10 +6729,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133036047</v>
+        <v>133036069</v>
       </c>
       <c r="B63" t="n">
-        <v>79923</v>
+        <v>57955</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6748,34 +6740,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>402804</v>
+        <v>402665</v>
       </c>
       <c r="R63" t="n">
-        <v>6825894</v>
+        <v>6825816</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133036051</v>
+        <v>133036118</v>
       </c>
       <c r="B66" t="n">
-        <v>57145</v>
+        <v>93206</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7051,31 +7051,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7083,10 +7078,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>402664</v>
+        <v>402624</v>
       </c>
       <c r="R66" t="n">
-        <v>6825645</v>
+        <v>6825913</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7127,6 +7122,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7145,10 +7141,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133036118</v>
+        <v>133036051</v>
       </c>
       <c r="B67" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7156,26 +7152,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7183,10 +7184,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>402624</v>
+        <v>402664</v>
       </c>
       <c r="R67" t="n">
-        <v>6825913</v>
+        <v>6825645</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7227,7 +7228,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133108956</v>
+        <v>133112214</v>
       </c>
       <c r="B75" t="n">
-        <v>79952</v>
+        <v>78999</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8004,34 +8004,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>402671</v>
+        <v>402724</v>
       </c>
       <c r="R75" t="n">
-        <v>6825689</v>
+        <v>6825783</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8088,65 +8088,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133108957</v>
+        <v>133108956</v>
       </c>
       <c r="B76" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärnen, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>402665</v>
+        <v>402671</v>
       </c>
       <c r="R76" t="n">
-        <v>6825701</v>
+        <v>6825689</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8178,7 +8170,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8188,7 +8180,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8215,45 +8207,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133112214</v>
+        <v>133108957</v>
       </c>
       <c r="B77" t="n">
-        <v>78999</v>
+        <v>57145</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Stor-Vargtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>402724</v>
+        <v>402665</v>
       </c>
       <c r="R77" t="n">
-        <v>6825783</v>
+        <v>6825701</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8310,12 +8310,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133112185</v>
+        <v>133108968</v>
       </c>
       <c r="B91" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9733,34 +9733,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>402814</v>
+        <v>402718</v>
       </c>
       <c r="R91" t="n">
-        <v>6825873</v>
+        <v>6825795</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9817,22 +9817,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133108968</v>
+        <v>133108960</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9840,21 +9840,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9864,10 +9864,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>402718</v>
+        <v>402802</v>
       </c>
       <c r="R92" t="n">
-        <v>6825795</v>
+        <v>6825824</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9936,10 +9936,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133108960</v>
+        <v>133112185</v>
       </c>
       <c r="B93" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9947,34 +9947,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>402802</v>
+        <v>402814</v>
       </c>
       <c r="R93" t="n">
-        <v>6825824</v>
+        <v>6825873</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10031,12 +10031,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10899,61 +10899,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133109707</v>
+        <v>133112197</v>
       </c>
       <c r="B102" t="n">
-        <v>57145</v>
+        <v>79091</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>402583</v>
+        <v>402778</v>
       </c>
       <c r="R102" t="n">
-        <v>6825567</v>
+        <v>6825767</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10985,7 +10969,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10995,7 +10979,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11010,12 +10994,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11236,45 +11220,61 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133112197</v>
+        <v>133109707</v>
       </c>
       <c r="B105" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>402778</v>
+        <v>402583</v>
       </c>
       <c r="R105" t="n">
-        <v>6825767</v>
+        <v>6825567</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11331,22 +11331,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133108961</v>
+        <v>133108981</v>
       </c>
       <c r="B106" t="n">
-        <v>79091</v>
+        <v>78999</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11354,21 +11354,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11378,10 +11378,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>402798</v>
+        <v>402836</v>
       </c>
       <c r="R106" t="n">
-        <v>6825844</v>
+        <v>6825888</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11450,10 +11450,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133108981</v>
+        <v>133109724</v>
       </c>
       <c r="B107" t="n">
-        <v>78999</v>
+        <v>79333</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11461,34 +11461,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>402836</v>
+        <v>402811</v>
       </c>
       <c r="R107" t="n">
-        <v>6825888</v>
+        <v>6825861</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11545,22 +11545,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133109724</v>
+        <v>133108961</v>
       </c>
       <c r="B108" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11568,34 +11568,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>402811</v>
+        <v>402798</v>
       </c>
       <c r="R108" t="n">
-        <v>6825861</v>
+        <v>6825844</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11652,22 +11652,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133112199</v>
+        <v>133112209</v>
       </c>
       <c r="B109" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>402724</v>
+        <v>402689</v>
       </c>
       <c r="R109" t="n">
-        <v>6825890</v>
+        <v>6825895</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11771,7 +11771,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133108963</v>
+        <v>133112199</v>
       </c>
       <c r="B110" t="n">
         <v>79090</v>
@@ -11802,14 +11802,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>402805</v>
+        <v>402724</v>
       </c>
       <c r="R110" t="n">
-        <v>6825842</v>
+        <v>6825890</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11866,22 +11866,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133112209</v>
+        <v>133108963</v>
       </c>
       <c r="B111" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11889,34 +11889,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>402689</v>
+        <v>402805</v>
       </c>
       <c r="R111" t="n">
-        <v>6825895</v>
+        <v>6825842</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11948,7 +11948,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11973,12 +11973,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12092,10 +12092,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133108982</v>
+        <v>133109722</v>
       </c>
       <c r="B113" t="n">
-        <v>78340</v>
+        <v>79333</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12103,34 +12103,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>402799</v>
+        <v>402811</v>
       </c>
       <c r="R113" t="n">
-        <v>6825819</v>
+        <v>6825852</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12187,22 +12187,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133109722</v>
+        <v>133108982</v>
       </c>
       <c r="B114" t="n">
-        <v>79333</v>
+        <v>78340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12210,34 +12210,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>402811</v>
+        <v>402799</v>
       </c>
       <c r="R114" t="n">
-        <v>6825852</v>
+        <v>6825819</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12294,12 +12294,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12948,10 +12948,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133108955</v>
+        <v>133112194</v>
       </c>
       <c r="B121" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12959,34 +12959,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>402804</v>
+        <v>402728</v>
       </c>
       <c r="R121" t="n">
-        <v>6825841</v>
+        <v>6825870</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13043,22 +13043,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133112194</v>
+        <v>133108955</v>
       </c>
       <c r="B122" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13066,34 +13066,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>402728</v>
+        <v>402804</v>
       </c>
       <c r="R122" t="n">
-        <v>6825870</v>
+        <v>6825841</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13150,12 +13150,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>

--- a/artfynd/A 16123-2026 artfynd.xlsx
+++ b/artfynd/A 16123-2026 artfynd.xlsx
@@ -1257,53 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133036059</v>
+        <v>133036030</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402611</v>
+        <v>402655</v>
       </c>
       <c r="R8" t="n">
-        <v>6825851</v>
+        <v>6825813</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133036030</v>
+        <v>133036106</v>
       </c>
       <c r="B9" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1373,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1397,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402655</v>
+        <v>402810</v>
       </c>
       <c r="R9" t="n">
-        <v>6825813</v>
+        <v>6825893</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,45 +1451,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133036106</v>
+        <v>133036059</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402810</v>
+        <v>402611</v>
       </c>
       <c r="R10" t="n">
-        <v>6825893</v>
+        <v>6825851</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133036031</v>
+        <v>133036044</v>
       </c>
       <c r="B12" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402676</v>
+        <v>402624</v>
       </c>
       <c r="R12" t="n">
-        <v>6825820</v>
+        <v>6825848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133036044</v>
+        <v>133036031</v>
       </c>
       <c r="B13" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402624</v>
+        <v>402676</v>
       </c>
       <c r="R13" t="n">
-        <v>6825848</v>
+        <v>6825820</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133036029</v>
+        <v>133036103</v>
       </c>
       <c r="B14" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402631</v>
+        <v>402700</v>
       </c>
       <c r="R14" t="n">
-        <v>6825844</v>
+        <v>6825867</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133036023</v>
+        <v>133036029</v>
       </c>
       <c r="B15" t="n">
         <v>79952</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402479</v>
+        <v>402631</v>
       </c>
       <c r="R15" t="n">
-        <v>6825791</v>
+        <v>6825844</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133036103</v>
+        <v>133036023</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402700</v>
+        <v>402479</v>
       </c>
       <c r="R16" t="n">
-        <v>6825867</v>
+        <v>6825791</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,45 +2243,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133036019</v>
+        <v>133036054</v>
       </c>
       <c r="B18" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>402701</v>
+        <v>402682</v>
       </c>
       <c r="R18" t="n">
-        <v>6825708</v>
+        <v>6825914</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,45 +2348,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133036024</v>
+        <v>133036056</v>
       </c>
       <c r="B19" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>402477</v>
+        <v>402473</v>
       </c>
       <c r="R19" t="n">
-        <v>6825770</v>
+        <v>6825788</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,53 +2453,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133036056</v>
+        <v>133036019</v>
       </c>
       <c r="B20" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>402473</v>
+        <v>402701</v>
       </c>
       <c r="R20" t="n">
-        <v>6825788</v>
+        <v>6825708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2542,53 +2550,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133036054</v>
+        <v>133036024</v>
       </c>
       <c r="B21" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402682</v>
+        <v>402477</v>
       </c>
       <c r="R21" t="n">
-        <v>6825914</v>
+        <v>6825770</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133036116</v>
+        <v>133036020</v>
       </c>
       <c r="B28" t="n">
-        <v>93206</v>
+        <v>79952</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>402698</v>
+        <v>402690</v>
       </c>
       <c r="R28" t="n">
-        <v>6825796</v>
+        <v>6825706</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133036020</v>
+        <v>133036116</v>
       </c>
       <c r="B29" t="n">
-        <v>79952</v>
+        <v>93206</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>402690</v>
+        <v>402698</v>
       </c>
       <c r="R29" t="n">
-        <v>6825706</v>
+        <v>6825796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3908,45 +3908,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133036095</v>
+        <v>133036057</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>402648</v>
+        <v>402565</v>
       </c>
       <c r="R35" t="n">
-        <v>6825618</v>
+        <v>6825861</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4005,7 +4013,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036057</v>
+        <v>133036058</v>
       </c>
       <c r="B36" t="n">
         <v>57145</v>
@@ -4048,10 +4056,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>402565</v>
+        <v>402615</v>
       </c>
       <c r="R36" t="n">
-        <v>6825861</v>
+        <v>6825849</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4110,10 +4118,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133036076</v>
+        <v>133036095</v>
       </c>
       <c r="B37" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4129,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4153,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>402671</v>
+        <v>402648</v>
       </c>
       <c r="R37" t="n">
-        <v>6825919</v>
+        <v>6825618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4207,7 +4215,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133036080</v>
+        <v>133036076</v>
       </c>
       <c r="B38" t="n">
         <v>79091</v>
@@ -4242,10 +4250,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>402781</v>
+        <v>402671</v>
       </c>
       <c r="R38" t="n">
-        <v>6825888</v>
+        <v>6825919</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,53 +4312,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133036058</v>
+        <v>133036080</v>
       </c>
       <c r="B39" t="n">
-        <v>57145</v>
+        <v>79091</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>402615</v>
+        <v>402781</v>
       </c>
       <c r="R39" t="n">
-        <v>6825849</v>
+        <v>6825888</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5400,10 +5400,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133036096</v>
+        <v>133036025</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5411,21 +5411,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>402697</v>
+        <v>402503</v>
       </c>
       <c r="R50" t="n">
-        <v>6825752</v>
+        <v>6825785</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133036025</v>
+        <v>133036096</v>
       </c>
       <c r="B51" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>402503</v>
+        <v>402697</v>
       </c>
       <c r="R51" t="n">
-        <v>6825785</v>
+        <v>6825752</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6527,10 +6527,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133036049</v>
+        <v>133036069</v>
       </c>
       <c r="B61" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6538,16 +6538,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6560,7 +6560,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>402692</v>
+        <v>402665</v>
       </c>
       <c r="R61" t="n">
-        <v>6825851</v>
+        <v>6825816</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133036047</v>
+        <v>133036049</v>
       </c>
       <c r="B62" t="n">
-        <v>79923</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6643,34 +6643,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>402804</v>
+        <v>402692</v>
       </c>
       <c r="R62" t="n">
-        <v>6825894</v>
+        <v>6825851</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6729,10 +6737,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133036069</v>
+        <v>133036047</v>
       </c>
       <c r="B63" t="n">
-        <v>57955</v>
+        <v>79923</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6740,42 +6748,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>402665</v>
+        <v>402804</v>
       </c>
       <c r="R63" t="n">
-        <v>6825816</v>
+        <v>6825894</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133108968</v>
+        <v>133112185</v>
       </c>
       <c r="B91" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9733,34 +9733,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>402718</v>
+        <v>402814</v>
       </c>
       <c r="R91" t="n">
-        <v>6825795</v>
+        <v>6825873</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9817,22 +9817,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133108960</v>
+        <v>133108968</v>
       </c>
       <c r="B92" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9840,21 +9840,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9864,10 +9864,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>402802</v>
+        <v>402718</v>
       </c>
       <c r="R92" t="n">
-        <v>6825824</v>
+        <v>6825795</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9936,10 +9936,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133112185</v>
+        <v>133108960</v>
       </c>
       <c r="B93" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9947,34 +9947,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>402814</v>
+        <v>402802</v>
       </c>
       <c r="R93" t="n">
-        <v>6825873</v>
+        <v>6825824</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10031,12 +10031,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10899,10 +10899,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133112197</v>
+        <v>133112182</v>
       </c>
       <c r="B102" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10910,21 +10910,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>402778</v>
+        <v>402723</v>
       </c>
       <c r="R102" t="n">
-        <v>6825767</v>
+        <v>6825890</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11006,7 +11006,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133112182</v>
+        <v>133108954</v>
       </c>
       <c r="B103" t="n">
         <v>79952</v>
@@ -11037,14 +11037,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>402723</v>
+        <v>402672</v>
       </c>
       <c r="R103" t="n">
-        <v>6825890</v>
+        <v>6825661</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11101,57 +11101,73 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133108954</v>
+        <v>133109707</v>
       </c>
       <c r="B104" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>402672</v>
+        <v>402583</v>
       </c>
       <c r="R104" t="n">
-        <v>6825661</v>
+        <v>6825567</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11183,7 +11199,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11193,7 +11209,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11208,73 +11224,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133109707</v>
+        <v>133112197</v>
       </c>
       <c r="B105" t="n">
-        <v>57145</v>
+        <v>79091</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>402583</v>
+        <v>402778</v>
       </c>
       <c r="R105" t="n">
-        <v>6825567</v>
+        <v>6825767</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11331,22 +11331,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133108981</v>
+        <v>133108961</v>
       </c>
       <c r="B106" t="n">
-        <v>78999</v>
+        <v>79091</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11354,21 +11354,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11378,10 +11378,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>402836</v>
+        <v>402798</v>
       </c>
       <c r="R106" t="n">
-        <v>6825888</v>
+        <v>6825844</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11450,10 +11450,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133109724</v>
+        <v>133108981</v>
       </c>
       <c r="B107" t="n">
-        <v>79333</v>
+        <v>78999</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11461,34 +11461,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>402811</v>
+        <v>402836</v>
       </c>
       <c r="R107" t="n">
-        <v>6825861</v>
+        <v>6825888</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11545,22 +11545,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133108961</v>
+        <v>133109724</v>
       </c>
       <c r="B108" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11568,34 +11568,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>402798</v>
+        <v>402811</v>
       </c>
       <c r="R108" t="n">
-        <v>6825844</v>
+        <v>6825861</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11652,12 +11652,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12948,10 +12948,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133112194</v>
+        <v>133108955</v>
       </c>
       <c r="B121" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12959,34 +12959,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>402728</v>
+        <v>402804</v>
       </c>
       <c r="R121" t="n">
-        <v>6825870</v>
+        <v>6825841</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13043,22 +13043,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133108955</v>
+        <v>133112194</v>
       </c>
       <c r="B122" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13066,34 +13066,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>402804</v>
+        <v>402728</v>
       </c>
       <c r="R122" t="n">
-        <v>6825841</v>
+        <v>6825870</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13150,12 +13150,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>

--- a/artfynd/A 16123-2026 artfynd.xlsx
+++ b/artfynd/A 16123-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133036111</v>
+        <v>133036105</v>
       </c>
       <c r="B2" t="n">
         <v>79333</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402735</v>
+        <v>402795</v>
       </c>
       <c r="R2" t="n">
-        <v>6825821</v>
+        <v>6825888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133036102</v>
+        <v>133036111</v>
       </c>
       <c r="B3" t="n">
         <v>79333</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402708</v>
+        <v>402735</v>
       </c>
       <c r="R3" t="n">
-        <v>6825844</v>
+        <v>6825821</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133036105</v>
+        <v>133036102</v>
       </c>
       <c r="B4" t="n">
         <v>79333</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402795</v>
+        <v>402708</v>
       </c>
       <c r="R4" t="n">
-        <v>6825888</v>
+        <v>6825844</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133036030</v>
+        <v>133036074</v>
       </c>
       <c r="B8" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402655</v>
+        <v>402612</v>
       </c>
       <c r="R8" t="n">
-        <v>6825813</v>
+        <v>6825742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,45 +1354,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133036106</v>
+        <v>133036059</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402810</v>
+        <v>402611</v>
       </c>
       <c r="R9" t="n">
-        <v>6825893</v>
+        <v>6825851</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,53 +1459,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133036059</v>
+        <v>133036030</v>
       </c>
       <c r="B10" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402611</v>
+        <v>402655</v>
       </c>
       <c r="R10" t="n">
-        <v>6825851</v>
+        <v>6825813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133036074</v>
+        <v>133036106</v>
       </c>
       <c r="B11" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402612</v>
+        <v>402810</v>
       </c>
       <c r="R11" t="n">
-        <v>6825742</v>
+        <v>6825893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133036044</v>
+        <v>133036031</v>
       </c>
       <c r="B12" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402624</v>
+        <v>402676</v>
       </c>
       <c r="R12" t="n">
-        <v>6825848</v>
+        <v>6825820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133036031</v>
+        <v>133036044</v>
       </c>
       <c r="B13" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402676</v>
+        <v>402624</v>
       </c>
       <c r="R13" t="n">
-        <v>6825820</v>
+        <v>6825848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133036103</v>
+        <v>133036029</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402700</v>
+        <v>402631</v>
       </c>
       <c r="R14" t="n">
-        <v>6825867</v>
+        <v>6825844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133036029</v>
+        <v>133036023</v>
       </c>
       <c r="B15" t="n">
         <v>79952</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402631</v>
+        <v>402479</v>
       </c>
       <c r="R15" t="n">
-        <v>6825844</v>
+        <v>6825791</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133036023</v>
+        <v>133036103</v>
       </c>
       <c r="B16" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402479</v>
+        <v>402700</v>
       </c>
       <c r="R16" t="n">
-        <v>6825791</v>
+        <v>6825867</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2453,10 +2453,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133036019</v>
+        <v>133036082</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>402701</v>
+        <v>402804</v>
       </c>
       <c r="R20" t="n">
-        <v>6825708</v>
+        <v>6825894</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133036024</v>
+        <v>133036019</v>
       </c>
       <c r="B21" t="n">
         <v>79952</v>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402477</v>
+        <v>402701</v>
       </c>
       <c r="R21" t="n">
-        <v>6825770</v>
+        <v>6825708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133036082</v>
+        <v>133036024</v>
       </c>
       <c r="B22" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402804</v>
+        <v>402477</v>
       </c>
       <c r="R22" t="n">
-        <v>6825894</v>
+        <v>6825770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133036100</v>
+        <v>133036121</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>78736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>402699</v>
+        <v>402677</v>
       </c>
       <c r="R24" t="n">
-        <v>6825854</v>
+        <v>6825909</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133036121</v>
+        <v>133036100</v>
       </c>
       <c r="B25" t="n">
-        <v>78736</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2949,21 +2949,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>402677</v>
+        <v>402699</v>
       </c>
       <c r="R25" t="n">
-        <v>6825909</v>
+        <v>6825854</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133036116</v>
+        <v>133036027</v>
       </c>
       <c r="B29" t="n">
-        <v>93206</v>
+        <v>79952</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>402698</v>
+        <v>402621</v>
       </c>
       <c r="R29" t="n">
-        <v>6825796</v>
+        <v>6825845</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,32 +3423,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133036027</v>
+        <v>133036116</v>
       </c>
       <c r="B30" t="n">
-        <v>79952</v>
+        <v>93206</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>402621</v>
+        <v>402698</v>
       </c>
       <c r="R30" t="n">
-        <v>6825845</v>
+        <v>6825796</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3908,53 +3908,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133036057</v>
+        <v>133036095</v>
       </c>
       <c r="B35" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>402565</v>
+        <v>402648</v>
       </c>
       <c r="R35" t="n">
-        <v>6825861</v>
+        <v>6825618</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4013,7 +4005,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036058</v>
+        <v>133036057</v>
       </c>
       <c r="B36" t="n">
         <v>57145</v>
@@ -4056,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>402615</v>
+        <v>402565</v>
       </c>
       <c r="R36" t="n">
-        <v>6825849</v>
+        <v>6825861</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4118,45 +4110,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133036095</v>
+        <v>133036058</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>402648</v>
+        <v>402615</v>
       </c>
       <c r="R37" t="n">
-        <v>6825618</v>
+        <v>6825849</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6321,10 +6321,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133036119</v>
+        <v>133036062</v>
       </c>
       <c r="B59" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6332,26 +6332,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6359,10 +6364,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>402643</v>
+        <v>402738</v>
       </c>
       <c r="R59" t="n">
-        <v>6825819</v>
+        <v>6825841</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6403,7 +6408,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6422,10 +6426,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133036062</v>
+        <v>133036119</v>
       </c>
       <c r="B60" t="n">
-        <v>57145</v>
+        <v>93206</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6433,31 +6437,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6465,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>402738</v>
+        <v>402643</v>
       </c>
       <c r="R60" t="n">
-        <v>6825841</v>
+        <v>6825819</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,6 +6508,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6527,10 +6527,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133036069</v>
+        <v>133036049</v>
       </c>
       <c r="B61" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6538,16 +6538,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6560,7 +6560,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>402665</v>
+        <v>402692</v>
       </c>
       <c r="R61" t="n">
-        <v>6825816</v>
+        <v>6825851</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133036049</v>
+        <v>133036069</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6643,16 +6643,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6665,7 +6665,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>402692</v>
+        <v>402665</v>
       </c>
       <c r="R62" t="n">
-        <v>6825851</v>
+        <v>6825816</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133036118</v>
+        <v>133036051</v>
       </c>
       <c r="B66" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7051,26 +7051,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7078,10 +7083,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>402624</v>
+        <v>402664</v>
       </c>
       <c r="R66" t="n">
-        <v>6825913</v>
+        <v>6825645</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7122,7 +7127,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7141,10 +7145,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133036051</v>
+        <v>133036118</v>
       </c>
       <c r="B67" t="n">
-        <v>57145</v>
+        <v>93206</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7152,31 +7156,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7184,10 +7183,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>402664</v>
+        <v>402624</v>
       </c>
       <c r="R67" t="n">
-        <v>6825645</v>
+        <v>6825913</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7228,6 +7227,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133112214</v>
+        <v>133108956</v>
       </c>
       <c r="B75" t="n">
-        <v>78999</v>
+        <v>79952</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8004,34 +8004,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>402724</v>
+        <v>402671</v>
       </c>
       <c r="R75" t="n">
-        <v>6825783</v>
+        <v>6825689</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8088,22 +8088,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133108956</v>
+        <v>133112214</v>
       </c>
       <c r="B76" t="n">
-        <v>79952</v>
+        <v>78999</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8111,34 +8111,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>402671</v>
+        <v>402724</v>
       </c>
       <c r="R76" t="n">
-        <v>6825689</v>
+        <v>6825783</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,12 +8195,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9508,10 +9508,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133112210</v>
+        <v>133109706</v>
       </c>
       <c r="B89" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>402750</v>
+        <v>402604</v>
       </c>
       <c r="R89" t="n">
-        <v>6825892</v>
+        <v>6825731</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9603,22 +9603,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133109706</v>
+        <v>133112210</v>
       </c>
       <c r="B90" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9626,21 +9626,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>402604</v>
+        <v>402750</v>
       </c>
       <c r="R90" t="n">
-        <v>6825731</v>
+        <v>6825892</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9710,22 +9710,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133112185</v>
+        <v>133108960</v>
       </c>
       <c r="B91" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9733,34 +9733,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>402814</v>
+        <v>402802</v>
       </c>
       <c r="R91" t="n">
-        <v>6825873</v>
+        <v>6825824</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9817,12 +9817,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9936,10 +9936,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133108960</v>
+        <v>133112185</v>
       </c>
       <c r="B93" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9947,34 +9947,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>402802</v>
+        <v>402814</v>
       </c>
       <c r="R93" t="n">
-        <v>6825824</v>
+        <v>6825873</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10031,12 +10031,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10150,10 +10150,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133112207</v>
+        <v>133112202</v>
       </c>
       <c r="B95" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>402731</v>
+        <v>402674</v>
       </c>
       <c r="R95" t="n">
-        <v>6825856</v>
+        <v>6825913</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10257,10 +10257,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133112202</v>
+        <v>133112207</v>
       </c>
       <c r="B96" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10268,21 +10268,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>402674</v>
+        <v>402731</v>
       </c>
       <c r="R96" t="n">
-        <v>6825913</v>
+        <v>6825856</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10685,45 +10685,61 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133108967</v>
+        <v>133109707</v>
       </c>
       <c r="B100" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>402719</v>
+        <v>402583</v>
       </c>
       <c r="R100" t="n">
-        <v>6825791</v>
+        <v>6825567</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10755,7 +10771,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10765,7 +10781,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10780,22 +10796,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133112208</v>
+        <v>133112197</v>
       </c>
       <c r="B101" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10803,21 +10819,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10827,10 +10843,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>402747</v>
+        <v>402778</v>
       </c>
       <c r="R101" t="n">
-        <v>6825862</v>
+        <v>6825767</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10862,7 +10878,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10872,7 +10888,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10899,10 +10915,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133112182</v>
+        <v>133108967</v>
       </c>
       <c r="B102" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10910,34 +10926,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>402723</v>
+        <v>402719</v>
       </c>
       <c r="R102" t="n">
-        <v>6825890</v>
+        <v>6825791</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10969,7 +10985,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10979,7 +10995,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10994,19 +11010,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133108954</v>
+        <v>133112182</v>
       </c>
       <c r="B103" t="n">
         <v>79952</v>
@@ -11037,14 +11053,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>402672</v>
+        <v>402723</v>
       </c>
       <c r="R103" t="n">
-        <v>6825661</v>
+        <v>6825890</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11076,7 +11092,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11086,7 +11102,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11101,73 +11117,57 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133109707</v>
+        <v>133112208</v>
       </c>
       <c r="B104" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>402583</v>
+        <v>402747</v>
       </c>
       <c r="R104" t="n">
-        <v>6825567</v>
+        <v>6825862</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11224,22 +11224,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133112197</v>
+        <v>133108954</v>
       </c>
       <c r="B105" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11247,34 +11247,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>402778</v>
+        <v>402672</v>
       </c>
       <c r="R105" t="n">
-        <v>6825767</v>
+        <v>6825661</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11331,22 +11331,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133108961</v>
+        <v>133109724</v>
       </c>
       <c r="B106" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11354,34 +11354,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>402798</v>
+        <v>402811</v>
       </c>
       <c r="R106" t="n">
-        <v>6825844</v>
+        <v>6825861</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11438,12 +11438,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133109724</v>
+        <v>133108961</v>
       </c>
       <c r="B108" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11568,34 +11568,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>402811</v>
+        <v>402798</v>
       </c>
       <c r="R108" t="n">
-        <v>6825861</v>
+        <v>6825844</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11652,22 +11652,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133112209</v>
+        <v>133112199</v>
       </c>
       <c r="B109" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>402689</v>
+        <v>402724</v>
       </c>
       <c r="R109" t="n">
-        <v>6825895</v>
+        <v>6825890</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11771,7 +11771,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133112199</v>
+        <v>133108963</v>
       </c>
       <c r="B110" t="n">
         <v>79090</v>
@@ -11802,14 +11802,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>402724</v>
+        <v>402805</v>
       </c>
       <c r="R110" t="n">
-        <v>6825890</v>
+        <v>6825842</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11866,22 +11866,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133108963</v>
+        <v>133112209</v>
       </c>
       <c r="B111" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11889,34 +11889,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>402805</v>
+        <v>402689</v>
       </c>
       <c r="R111" t="n">
-        <v>6825842</v>
+        <v>6825895</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11948,7 +11948,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11973,12 +11973,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12092,10 +12092,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133109722</v>
+        <v>133108982</v>
       </c>
       <c r="B113" t="n">
-        <v>79333</v>
+        <v>78340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12103,34 +12103,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>402811</v>
+        <v>402799</v>
       </c>
       <c r="R113" t="n">
-        <v>6825852</v>
+        <v>6825819</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12187,22 +12187,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133108982</v>
+        <v>133109722</v>
       </c>
       <c r="B114" t="n">
-        <v>78340</v>
+        <v>79333</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12210,34 +12210,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>402799</v>
+        <v>402811</v>
       </c>
       <c r="R114" t="n">
-        <v>6825819</v>
+        <v>6825852</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12294,12 +12294,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>

--- a/artfynd/A 16123-2026 artfynd.xlsx
+++ b/artfynd/A 16123-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133036105</v>
+        <v>133036111</v>
       </c>
       <c r="B2" t="n">
         <v>79333</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402795</v>
+        <v>402735</v>
       </c>
       <c r="R2" t="n">
-        <v>6825888</v>
+        <v>6825821</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133036111</v>
+        <v>133036102</v>
       </c>
       <c r="B3" t="n">
         <v>79333</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402735</v>
+        <v>402708</v>
       </c>
       <c r="R3" t="n">
-        <v>6825821</v>
+        <v>6825844</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133036102</v>
+        <v>133036105</v>
       </c>
       <c r="B4" t="n">
         <v>79333</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402708</v>
+        <v>402795</v>
       </c>
       <c r="R4" t="n">
-        <v>6825844</v>
+        <v>6825888</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1257,45 +1257,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133036074</v>
+        <v>133036059</v>
       </c>
       <c r="B8" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402612</v>
+        <v>402611</v>
       </c>
       <c r="R8" t="n">
-        <v>6825742</v>
+        <v>6825851</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,53 +1362,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133036059</v>
+        <v>133036030</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402611</v>
+        <v>402655</v>
       </c>
       <c r="R9" t="n">
-        <v>6825851</v>
+        <v>6825813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133036030</v>
+        <v>133036106</v>
       </c>
       <c r="B10" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402655</v>
+        <v>402810</v>
       </c>
       <c r="R10" t="n">
-        <v>6825813</v>
+        <v>6825893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133036106</v>
+        <v>133036074</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402810</v>
+        <v>402612</v>
       </c>
       <c r="R11" t="n">
-        <v>6825893</v>
+        <v>6825742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133036029</v>
+        <v>133036103</v>
       </c>
       <c r="B14" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402631</v>
+        <v>402700</v>
       </c>
       <c r="R14" t="n">
-        <v>6825844</v>
+        <v>6825867</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133036023</v>
+        <v>133036029</v>
       </c>
       <c r="B15" t="n">
         <v>79952</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402479</v>
+        <v>402631</v>
       </c>
       <c r="R15" t="n">
-        <v>6825791</v>
+        <v>6825844</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133036103</v>
+        <v>133036023</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402700</v>
+        <v>402479</v>
       </c>
       <c r="R16" t="n">
-        <v>6825867</v>
+        <v>6825791</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,53 +2243,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133036054</v>
+        <v>133036019</v>
       </c>
       <c r="B18" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>402682</v>
+        <v>402701</v>
       </c>
       <c r="R18" t="n">
-        <v>6825914</v>
+        <v>6825708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,53 +2340,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133036056</v>
+        <v>133036024</v>
       </c>
       <c r="B19" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>402473</v>
+        <v>402477</v>
       </c>
       <c r="R19" t="n">
-        <v>6825788</v>
+        <v>6825770</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2453,45 +2437,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133036082</v>
+        <v>133036054</v>
       </c>
       <c r="B20" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>402804</v>
+        <v>402682</v>
       </c>
       <c r="R20" t="n">
-        <v>6825894</v>
+        <v>6825914</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,45 +2542,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133036019</v>
+        <v>133036056</v>
       </c>
       <c r="B21" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402701</v>
+        <v>402473</v>
       </c>
       <c r="R21" t="n">
-        <v>6825708</v>
+        <v>6825788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133036024</v>
+        <v>133036082</v>
       </c>
       <c r="B22" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402477</v>
+        <v>402804</v>
       </c>
       <c r="R22" t="n">
-        <v>6825770</v>
+        <v>6825894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133036121</v>
+        <v>133036100</v>
       </c>
       <c r="B24" t="n">
-        <v>78736</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>402677</v>
+        <v>402699</v>
       </c>
       <c r="R24" t="n">
-        <v>6825909</v>
+        <v>6825854</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133036100</v>
+        <v>133036121</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>78736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2949,21 +2949,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>402699</v>
+        <v>402677</v>
       </c>
       <c r="R25" t="n">
-        <v>6825854</v>
+        <v>6825909</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133036027</v>
+        <v>133036116</v>
       </c>
       <c r="B29" t="n">
-        <v>79952</v>
+        <v>93206</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>402621</v>
+        <v>402698</v>
       </c>
       <c r="R29" t="n">
-        <v>6825845</v>
+        <v>6825796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,32 +3423,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133036116</v>
+        <v>133036027</v>
       </c>
       <c r="B30" t="n">
-        <v>93206</v>
+        <v>79952</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>402698</v>
+        <v>402621</v>
       </c>
       <c r="R30" t="n">
-        <v>6825796</v>
+        <v>6825845</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3908,45 +3908,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133036095</v>
+        <v>133036057</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>402648</v>
+        <v>402565</v>
       </c>
       <c r="R35" t="n">
-        <v>6825618</v>
+        <v>6825861</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4005,7 +4013,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036057</v>
+        <v>133036058</v>
       </c>
       <c r="B36" t="n">
         <v>57145</v>
@@ -4048,10 +4056,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>402565</v>
+        <v>402615</v>
       </c>
       <c r="R36" t="n">
-        <v>6825861</v>
+        <v>6825849</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4110,53 +4118,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133036058</v>
+        <v>133036076</v>
       </c>
       <c r="B37" t="n">
-        <v>57145</v>
+        <v>79091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>402615</v>
+        <v>402671</v>
       </c>
       <c r="R37" t="n">
-        <v>6825849</v>
+        <v>6825919</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133036076</v>
+        <v>133036080</v>
       </c>
       <c r="B38" t="n">
         <v>79091</v>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>402671</v>
+        <v>402781</v>
       </c>
       <c r="R38" t="n">
-        <v>6825919</v>
+        <v>6825888</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133036080</v>
+        <v>133036095</v>
       </c>
       <c r="B39" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>402781</v>
+        <v>402648</v>
       </c>
       <c r="R39" t="n">
-        <v>6825888</v>
+        <v>6825618</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4603,53 +4603,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133036055</v>
+        <v>133036040</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>79923</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>402543</v>
+        <v>402687</v>
       </c>
       <c r="R42" t="n">
-        <v>6825867</v>
+        <v>6825894</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4708,45 +4700,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133036040</v>
+        <v>133036055</v>
       </c>
       <c r="B43" t="n">
-        <v>79923</v>
+        <v>57145</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>402687</v>
+        <v>402543</v>
       </c>
       <c r="R43" t="n">
-        <v>6825894</v>
+        <v>6825867</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6527,10 +6527,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133036049</v>
+        <v>133036047</v>
       </c>
       <c r="B61" t="n">
-        <v>57958</v>
+        <v>79923</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6538,42 +6538,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>402692</v>
+        <v>402804</v>
       </c>
       <c r="R61" t="n">
-        <v>6825851</v>
+        <v>6825894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,10 +6729,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133036047</v>
+        <v>133036049</v>
       </c>
       <c r="B63" t="n">
-        <v>79923</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6748,34 +6740,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>402804</v>
+        <v>402692</v>
       </c>
       <c r="R63" t="n">
-        <v>6825894</v>
+        <v>6825851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133036051</v>
+        <v>133036118</v>
       </c>
       <c r="B66" t="n">
-        <v>57145</v>
+        <v>93206</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7051,31 +7051,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7083,10 +7078,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>402664</v>
+        <v>402624</v>
       </c>
       <c r="R66" t="n">
-        <v>6825645</v>
+        <v>6825913</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7127,6 +7122,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7145,10 +7141,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133036118</v>
+        <v>133036051</v>
       </c>
       <c r="B67" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7156,26 +7152,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7183,10 +7184,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>402624</v>
+        <v>402664</v>
       </c>
       <c r="R67" t="n">
-        <v>6825913</v>
+        <v>6825645</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7227,7 +7228,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8322,45 +8322,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133108973</v>
+        <v>133112191</v>
       </c>
       <c r="B78" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>402819</v>
+        <v>402669</v>
       </c>
       <c r="R78" t="n">
-        <v>6825855</v>
+        <v>6825647</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8392,7 +8400,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8402,7 +8410,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8417,22 +8425,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133108965</v>
+        <v>133108973</v>
       </c>
       <c r="B79" t="n">
-        <v>78340</v>
+        <v>79333</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8440,21 +8448,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8464,10 +8472,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>402810</v>
+        <v>402819</v>
       </c>
       <c r="R79" t="n">
-        <v>6825852</v>
+        <v>6825855</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8507,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8509,7 +8517,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8536,53 +8544,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133112191</v>
+        <v>133108965</v>
       </c>
       <c r="B80" t="n">
-        <v>57145</v>
+        <v>78340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>402669</v>
+        <v>402810</v>
       </c>
       <c r="R80" t="n">
-        <v>6825647</v>
+        <v>6825852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8639,12 +8639,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9508,10 +9508,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133109706</v>
+        <v>133112210</v>
       </c>
       <c r="B89" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>402604</v>
+        <v>402750</v>
       </c>
       <c r="R89" t="n">
-        <v>6825731</v>
+        <v>6825892</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9603,22 +9603,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133112210</v>
+        <v>133109706</v>
       </c>
       <c r="B90" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9626,21 +9626,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>402750</v>
+        <v>402604</v>
       </c>
       <c r="R90" t="n">
-        <v>6825892</v>
+        <v>6825731</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9710,22 +9710,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133108960</v>
+        <v>133108968</v>
       </c>
       <c r="B91" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9733,21 +9733,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>402802</v>
+        <v>402718</v>
       </c>
       <c r="R91" t="n">
-        <v>6825824</v>
+        <v>6825795</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9829,10 +9829,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133108968</v>
+        <v>133112185</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9840,34 +9840,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>402718</v>
+        <v>402814</v>
       </c>
       <c r="R92" t="n">
-        <v>6825795</v>
+        <v>6825873</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9924,22 +9924,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133112185</v>
+        <v>133108960</v>
       </c>
       <c r="B93" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9947,34 +9947,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>402814</v>
+        <v>402802</v>
       </c>
       <c r="R93" t="n">
-        <v>6825873</v>
+        <v>6825824</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10031,12 +10031,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133112197</v>
+        <v>133108967</v>
       </c>
       <c r="B101" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10819,34 +10819,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>402778</v>
+        <v>402719</v>
       </c>
       <c r="R101" t="n">
-        <v>6825767</v>
+        <v>6825791</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10903,22 +10903,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133108967</v>
+        <v>133112182</v>
       </c>
       <c r="B102" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>402719</v>
+        <v>402723</v>
       </c>
       <c r="R102" t="n">
-        <v>6825791</v>
+        <v>6825890</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11010,22 +11010,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133112182</v>
+        <v>133112208</v>
       </c>
       <c r="B103" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11033,21 +11033,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11057,10 +11057,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>402723</v>
+        <v>402747</v>
       </c>
       <c r="R103" t="n">
-        <v>6825890</v>
+        <v>6825862</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11129,10 +11129,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133112208</v>
+        <v>133108954</v>
       </c>
       <c r="B104" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11140,34 +11140,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Brunnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>402747</v>
+        <v>402672</v>
       </c>
       <c r="R104" t="n">
-        <v>6825862</v>
+        <v>6825661</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11224,22 +11224,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133108954</v>
+        <v>133112197</v>
       </c>
       <c r="B105" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11247,34 +11247,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Brunnkällan, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>402672</v>
+        <v>402778</v>
       </c>
       <c r="R105" t="n">
-        <v>6825661</v>
+        <v>6825767</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11331,12 +11331,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11450,10 +11450,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133108981</v>
+        <v>133108961</v>
       </c>
       <c r="B107" t="n">
-        <v>78999</v>
+        <v>79091</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11461,21 +11461,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11485,10 +11485,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>402836</v>
+        <v>402798</v>
       </c>
       <c r="R107" t="n">
-        <v>6825888</v>
+        <v>6825844</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11557,10 +11557,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133108961</v>
+        <v>133108981</v>
       </c>
       <c r="B108" t="n">
-        <v>79091</v>
+        <v>78999</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11592,10 +11592,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>402798</v>
+        <v>402836</v>
       </c>
       <c r="R108" t="n">
-        <v>6825844</v>
+        <v>6825888</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 16123-2026 artfynd.xlsx
+++ b/artfynd/A 16123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108981</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112214</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036116</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036118</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036119</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036095</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036096</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036098</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036099</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036100</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036102</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036103</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036104</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036105</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2155,6 +2230,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036106</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036111</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2353,6 +2438,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036114</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2460,6 +2550,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108966</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108967</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2674,6 +2774,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108968</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2781,6 +2886,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108969</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2888,6 +2998,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108970</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108972</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3102,6 +3222,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108973</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3209,6 +3334,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108974</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3316,6 +3446,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109718</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3423,6 +3558,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109719</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3530,6 +3670,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109721</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3637,6 +3782,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109722</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3744,6 +3894,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109723</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3851,6 +4006,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109724</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3958,6 +4118,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112205</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4065,6 +4230,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112206</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4172,6 +4342,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112207</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4279,6 +4454,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112208</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4386,6 +4566,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112209</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4493,6 +4678,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112210</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4600,6 +4790,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112211</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4707,6 +4902,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112212</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4804,6 +5004,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036121</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4901,6 +5106,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036083</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5008,6 +5218,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108962</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5115,6 +5330,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108963</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5222,6 +5442,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108964</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5329,6 +5554,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109716</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5436,6 +5666,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112199</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5543,6 +5778,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112200</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5650,6 +5890,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112202</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5747,6 +5992,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036019</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5844,6 +6094,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036020</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5941,6 +6196,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036021</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6038,6 +6298,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036023</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6135,6 +6400,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036024</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6232,6 +6502,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6329,6 +6604,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036027</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6426,6 +6706,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036029</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6523,6 +6808,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036030</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6620,6 +6910,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036031</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6717,6 +7012,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036032</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6818,6 +7118,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036033</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6915,6 +7220,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036034</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7022,6 +7332,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108954</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7129,6 +7444,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108955</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7236,6 +7556,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108956</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7343,6 +7668,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109704</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7450,6 +7780,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112182</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7557,6 +7892,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112183</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7664,6 +8004,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112185</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7771,6 +8116,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108965</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7878,6 +8228,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108982</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7986,6 +8341,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112215</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8091,6 +8451,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036069</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8196,6 +8561,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036070</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8301,6 +8671,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036071</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8406,6 +8781,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036049</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8511,6 +8891,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036050</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8616,6 +9001,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036051</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8721,6 +9111,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036052</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8826,6 +9221,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036053</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8931,6 +9331,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036054</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9036,6 +9441,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036055</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9141,6 +9551,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036056</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9246,6 +9661,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036057</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9351,6 +9771,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036058</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9456,6 +9881,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036059</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9561,6 +9991,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036060</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9666,6 +10101,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036062</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9776,6 +10216,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036063</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9891,6 +10336,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108957</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10014,6 +10464,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109707</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10129,6 +10584,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112191</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10234,6 +10694,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036084</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10339,6 +10804,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036085</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10436,6 +10906,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036073</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10533,6 +11008,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036074</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10630,6 +11110,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036075</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10727,6 +11212,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036076</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10824,6 +11314,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036077</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10921,6 +11416,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036078</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11018,6 +11518,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036079</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11115,6 +11620,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036080</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11212,6 +11722,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036081</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11309,6 +11824,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036082</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11416,6 +11936,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108959</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11523,6 +12048,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108960</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11630,6 +12160,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133108961</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11737,6 +12272,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109714</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11845,6 +12385,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109715</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11952,6 +12497,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112192</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12059,6 +12609,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112194</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12166,6 +12721,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112197</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12273,6 +12833,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112198</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12370,6 +12935,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036039</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12467,6 +13037,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036040</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12564,6 +13139,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036041</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12665,6 +13245,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036042</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12762,6 +13347,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036044</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12859,6 +13449,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036045</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12956,6 +13551,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036046</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13053,6 +13653,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036047</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13160,6 +13765,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109706</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13267,6 +13877,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112188</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13374,8 +13989,138 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133112189</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>